--- a/tests/fixtures/dimensions/foreign.xlsx
+++ b/tests/fixtures/dimensions/foreign.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmplxbp8eye\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmpcud89dlp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A85B77A-1A67-40F3-BC55-064F1491C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B46BAA9-3E8F-4E9F-8E9D-53933F1A5FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="19440" windowHeight="11220" xr2:uid="{2354992F-22EF-4ABE-8308-F224E40BE026}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="19440" windowHeight="11220" xr2:uid="{B0299607-09CF-4D9F-AF87-312B414D5C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28DFB283-69B8-4523-8DE8-B41620023AEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CF54C3-D402-4200-A6C6-F8FA5FF63ECE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/tests/fixtures/dimensions/foreign.xlsx
+++ b/tests/fixtures/dimensions/foreign.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\AppData\Local\Temp\tmpcud89dlp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{0B46BAA9-3E8F-4E9F-8E9D-53933F1A5FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="19440" windowHeight="11220" xr2:uid="{B0299607-09CF-4D9F-AF87-312B414D5C54}"/>
